--- a/test_cases.xlsx
+++ b/test_cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Dokumentumok\GitHub\se-lab4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA1082EF-BFA7-464E-AB01-7BFE1A2D39E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E358D69-77E4-4E85-B4F3-CC67BC74E9AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{610E781D-AB94-48C9-ABEA-C63577EC3207}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="19">
   <si>
     <t>Tesztelt követelmény</t>
   </si>
@@ -293,6 +293,9 @@
   </si>
   <si>
     <t>teszt hiba, üres sort is beolvasta az output végén</t>
+  </si>
+  <si>
+    <t>van legalább 1 torpedó a hajóban 1 a secondary store-ban</t>
   </si>
 </sst>
 </file>
@@ -685,10 +688,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE8E9349-5DDE-4347-A986-E3C0DFDA2182}">
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="60">
+    <row r="1" spans="1:17" ht="60">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -719,8 +722,14 @@
       <c r="N1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="P1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="2" spans="1:14" ht="135">
+    <row r="2" spans="1:17" ht="150">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -751,8 +760,14 @@
       <c r="N2" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="P2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" spans="1:14" ht="160.5">
+    <row r="3" spans="1:17" ht="160.5">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -783,8 +798,14 @@
       <c r="N3" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="P3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="4" spans="1:14" ht="130.5">
+    <row r="4" spans="1:17" ht="130.5">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -815,8 +836,14 @@
       <c r="N4" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="P4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:14" ht="120">
+    <row r="5" spans="1:17" ht="120">
       <c r="K5" s="1" t="s">
         <v>17</v>
       </c>
